--- a/Result/profitability/3296.xlsx
+++ b/Result/profitability/3296.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.29</v>
       </c>
       <c r="M2" t="n">
-        <v>0.12375</v>
+        <v>0.15</v>
       </c>
       <c r="N2" t="n">
-        <v>20.1675</v>
+        <v>19.7025</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="N3" t="n">
-        <v>18.08875</v>
+        <v>17.775</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,16 +899,16 @@
         <v>1.15</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2125</v>
+        <v>0.22</v>
       </c>
       <c r="N4" t="n">
-        <v>17.4475</v>
+        <v>16.87125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.32</v>
       </c>
       <c r="M5" t="n">
-        <v>0.23875</v>
+        <v>0.18875</v>
       </c>
       <c r="N5" t="n">
-        <v>16.26625</v>
+        <v>15.69625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.28</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2025</v>
+        <v>0.2225</v>
       </c>
       <c r="N6" t="n">
-        <v>15.2675</v>
+        <v>15.02875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.64</v>
       </c>
       <c r="M7" t="n">
-        <v>0.28125</v>
+        <v>0.31125</v>
       </c>
       <c r="N7" t="n">
-        <v>15.23125</v>
+        <v>15.0875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.08</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4249999999999999</v>
+        <v>0.4925</v>
       </c>
       <c r="N8" t="n">
-        <v>15.6825</v>
+        <v>16.14</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1415,7 +1415,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" t="n">
         <v>98.3</v>
@@ -1645,7 +1645,7 @@
         <v>0.55</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6174999999999999</v>
+        <v>0.6175</v>
       </c>
       <c r="N10" t="n">
         <v>16.75375</v>
@@ -2026,7 +2026,7 @@
         <v>-0.19</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5475</v>
+        <v>0.5475000000000001</v>
       </c>
       <c r="N13" t="n">
         <v>18.7075</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3296</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>488</v>
+      </c>
+      <c r="D75" t="n">
+        <v>400</v>
+      </c>
+      <c r="E75" t="n">
+        <v>88</v>
+      </c>
+      <c r="F75" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="G75" t="n">
+        <v>13</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.71%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>16</v>
+      </c>
+      <c r="K75" t="n">
+        <v>16</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.10875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.459459459459459</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.659999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2541666666666667</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.3999999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.7017543859649122</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-4.560000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2015915119363396</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
